--- a/tesis-ciadi/ANÁLISIS-CAPITAL-CIADI.xlsx
+++ b/tesis-ciadi/ANÁLISIS-CAPITAL-CIADI.xlsx
@@ -7,14 +7,17 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ANÁLISIS CENTRAL" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ESTADOS Y PAÍSES" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="PAÍSES Y CLASIFICACIÓN" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="FLUJOS DE CAPITAL BM" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CONCLUSIONES" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TABLA MAESTRA RESULTADOS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MONTOS Y ÁRBITROS" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="ANÁLISIS CENTRAL" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ESTADOS Y PAÍSES" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="PAÍSES Y CLASIFICACIÓN" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="FLUJOS DE CAPITAL BM" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'PAÍSES Y CLASIFICACIÓN'!$A$1:$M$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'FLUJOS DE CAPITAL BM'!$A$1:$AZ$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PAÍSES Y CLASIFICACIÓN'!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'FLUJOS DE CAPITAL BM'!$A$1:$AZ$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -26,7 +29,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -122,8 +125,50 @@
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00444444"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00555555"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="25">
+  <fills count="45">
     <fill>
       <patternFill/>
     </fill>
@@ -252,8 +297,116 @@
         <bgColor rgb="007B0041"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+        <bgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4B8B8"/>
+        <bgColor rgb="00F4B8B8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+        <bgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+        <bgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00595959"/>
+        <bgColor rgb="00595959"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="000D2137"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D5F0F0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFB8B8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8F7C5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="008B0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001D6A2A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C55A11"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004B0082"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00555555"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -275,11 +428,146 @@
         <color rgb="00CCCCCC"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BBBBBB"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BBBBBB"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00BBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="162">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -479,6 +767,248 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="29" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="21" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="25" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="20" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="26" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="29" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="35" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="9" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="21" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="35" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="37" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="38" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="39" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="40" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="41" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="42" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="43" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="44" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -845,6 +1375,4011 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="152" t="inlineStr">
+        <is>
+          <t>CONCLUSIONES DE LA INVESTIGACIÓN — LAUDOS CIADI 2000-2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="153" t="inlineStr">
+        <is>
+          <t>A. HIPÓTESIS CENTRAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="55" customHeight="1">
+      <c r="A4" s="154" t="inlineStr">
+        <is>
+          <t>C1</t>
+        </is>
+      </c>
+      <c r="B4" s="155" t="inlineStr">
+        <is>
+          <t>Los importadores netos concentran el 80.9% de los casos CIADI (283/350) y el 78.7% de las condenas absolutas (129/164). El sistema pesa desproporcionalmente sobre los Estados que más necesitan capital.</t>
+        </is>
+      </c>
+      <c r="C4" s="156" t="inlineStr">
+        <is>
+          <t>Exportador: 60 casos, 33 condenas. Importador: 283 casos, 129 condenas. Fuente: BM + UNCTAD.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="55" customHeight="1">
+      <c r="A5" s="154" t="inlineStr">
+        <is>
+          <t>C2</t>
+        </is>
+      </c>
+      <c r="B5" s="155" t="inlineStr">
+        <is>
+          <t>La tasa de condena por caso es mayor en exportadores (55.0%) que en importadores (45.6%), PERO esto se explica casi enteramente por España (25 casos, 92% tasa). Sin España, exportadores: 28.6% — por debajo de importadores.</t>
+        </is>
+      </c>
+      <c r="C5" s="156" t="inlineStr">
+        <is>
+          <t>España excluida: exportadores 35 casos / 10 condenas (28.6%). Con España: 60 / 33 (55%). El caso España distorsiona la variable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="55" customHeight="1">
+      <c r="A6" s="154" t="inlineStr">
+        <is>
+          <t>C3</t>
+        </is>
+      </c>
+      <c r="B6" s="155" t="inlineStr">
+        <is>
+          <t>Las 14 condenas "sin daños" del período recaen exclusivamente sobre importadores netos (0 sobre exportadores). Los árbitros reconocen la violación pero niegan compensación solo cuando el demandado es importador.</t>
+        </is>
+      </c>
+      <c r="C6" s="156" t="inlineStr">
+        <is>
+          <t>Importadores: 115 cd + 14 sd + 154 abs. Exportadores: 33 cd + 0 sd + 27 abs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="157" t="inlineStr">
+        <is>
+          <t>B. CASO ESPAÑA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="55" customHeight="1">
+      <c r="A9" s="154" t="inlineStr">
+        <is>
+          <t>C4</t>
+        </is>
+      </c>
+      <c r="B9" s="155" t="inlineStr">
+        <is>
+          <t>España es un outlier no generalizable. Sus 25 casos (23 condenas, 92%) son todos post-2012 por recorte a energías renovables bajo el ECT. No refleja un patrón sistémico de exportadores que pierden más.</t>
+        </is>
+      </c>
+      <c r="C9" s="156" t="inlineStr">
+        <is>
+          <t>Todos los casos España: 2012-2016. Tratado: ECT. Sector: electricidad/renovables. Recomendación: tratarlo como variable de control separada en la tesis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="55" customHeight="1">
+      <c r="A10" s="154" t="inlineStr">
+        <is>
+          <t>C5</t>
+        </is>
+      </c>
+      <c r="B10" s="155" t="inlineStr">
+        <is>
+          <t>El ECT (Energy Charter Treaty) es el tratado más litigioso con 44 casos y 60.8% de tasa de condena. Exportadores bajo ECT: 83.3% tasa. Importadores bajo ECT: 28.6%. Sin ECT, exportadores tienen solo 26.7% vs 46.5% de importadores — relación invertida.</t>
+        </is>
+      </c>
+      <c r="C10" s="156" t="inlineStr">
+        <is>
+          <t>Con ECT: 44 casos, 31 condenas (60.8%). Sin ECT: 299 casos, 133 condenas (44.5%). El ECT explica el hallazgo contra-intuitivo sobre exportadores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="158" t="inlineStr">
+        <is>
+          <t>C. ACTORES ESPECÍFICOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="55" customHeight="1">
+      <c r="A13" s="154" t="inlineStr">
+        <is>
+          <t>C6</t>
+        </is>
+      </c>
+      <c r="B13" s="155" t="inlineStr">
+        <is>
+          <t>América Latina es la región más expuesta: 110 casos, 56.4% tasa de condena. Venezuela (26/65.4%), Argentina (24/79.2%) y México (13/61.5%) encabezan. Todos son importadores netos.</t>
+        </is>
+      </c>
+      <c r="C13" s="156" t="inlineStr">
+        <is>
+          <t>Argentina: mayor tasa absoluta. Venezuela: caso ConocoPhillips (USD 8.366 mill.), mayor condena del período. México: NAFTA como vector principal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="55" customHeight="1">
+      <c r="A14" s="154" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="B14" s="155" t="inlineStr">
+        <is>
+          <t>EE.UU. es el mayor inversor demandante (62 casos, 37.1% tasa). Nunca fue condenado como estado demandado en el período. Paradoja: es exportador neto pero con margen mínimo (+USD 2.164 mill./año).</t>
+        </is>
+      </c>
+      <c r="C14" s="156" t="inlineStr">
+        <is>
+          <t>EE.UU. como demandante: 23 condenas. Como demandado: 0 condenas. Margen neto FDI 2000-2022: apenas positivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="55" customHeight="1">
+      <c r="A15" s="154" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="B15" s="155" t="inlineStr">
+        <is>
+          <t>Países Bajos: 28 casos como inversor, 13 condenas (46.4%). Fenómeno de treaty shopping: holdings holandeses canalizan inversión real de EE.UU., Rusia, España y otros países. La nacionalidad nominal del inversor no equivale al origen real del capital.</t>
+        </is>
+      </c>
+      <c r="C15" s="156" t="inlineStr">
+        <is>
+          <t>NL demanda a: Venezuela (4), Croatia (3), Turkey (3), Spain (3), Kazakhstan (2). El inversor "holandés" real suele ser una filial de empresa estadounidense o rusa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="55" customHeight="1">
+      <c r="A16" s="154" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="B16" s="155" t="inlineStr">
+        <is>
+          <t>China es el mayor importador neto del mundo (-USD 93.956 mill./año) pero tiene exposición mínima al CIADI. La exposición no es solo función de flujos de capital sino de la arquitectura de TBIs aceptada por el Estado.</t>
+        </is>
+      </c>
+      <c r="C16" s="156" t="inlineStr">
+        <is>
+          <t>China importa 4x más que el segundo importador (México: -21.380). Su política de no sometimiento al CIADI la excluye del universo. Caso metodológico relevante para la tesis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="159" t="inlineStr">
+        <is>
+          <t>D. SISTEMA CIADI</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="55" customHeight="1">
+      <c r="A19" s="154" t="inlineStr">
+        <is>
+          <t>C10</t>
+        </is>
+      </c>
+      <c r="B19" s="155" t="inlineStr">
+        <is>
+          <t>Tendencia decreciente de condenas en el tiempo: 49.1% (2000-2007) → 49.7% (2008-2015) → 38.0% (2016-2022). Los estados mejoran su defensa y/o los árbitros son más cautelosos con el tiempo.</t>
+        </is>
+      </c>
+      <c r="C19" s="156" t="inlineStr">
+        <is>
+          <t>Puede correlacionarse con el surgimiento de nuevas defensas estatales (estado de necesidad, necesidad económica), y la reacción institucional post-crisis 2001-2008.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="55" customHeight="1">
+      <c r="A20" s="154" t="inlineStr">
+        <is>
+          <t>C11</t>
+        </is>
+      </c>
+      <c r="B20" s="155" t="inlineStr">
+        <is>
+          <t>Energía y minería: 118 casos (33.7% del universo), 56.8% de tasa de condena. Sector agua: 14 casos, 78.6% de tasa — la más alta de todos los sectores.</t>
+        </is>
+      </c>
+      <c r="C20" s="156" t="inlineStr">
+        <is>
+          <t>Los sectores donde el estado regula interés público quedan más expuestos al CIADI. Regulación sectorial como gatillo de demandas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="55" customHeight="1">
+      <c r="A21" s="154" t="inlineStr">
+        <is>
+          <t>C12</t>
+        </is>
+      </c>
+      <c r="B21" s="155" t="inlineStr">
+        <is>
+          <t>El Trato Justo y Equitativo (TJE) es la violación más alegada y más exitosa. Aparece en la mayoría de las condenas, solo o combinado con expropiación. Es el vector de expansión de la responsabilidad estatal.</t>
+        </is>
+      </c>
+      <c r="C21" s="156" t="inlineStr">
+        <is>
+          <t>TJE solo: 43 condenas. TJE+Expropiación: 52+. La cláusula de "expectativas legítimas" del inversor expande el concepto de forma pretoriana.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="55" customHeight="1">
+      <c r="A22" s="154" t="inlineStr">
+        <is>
+          <t>C13</t>
+        </is>
+      </c>
+      <c r="B22" s="155" t="inlineStr">
+        <is>
+          <t>Brigitte Stern fue nombrada por estados demandados 52 veces — el árbitro más usado como defensa estatal. Gabrielle Kaufmann-Kohler presidió 20 tribunales. Esta concentración en pocos árbitros es un hallazgo sobre el funcionamiento del sistema.</t>
+        </is>
+      </c>
+      <c r="C22" s="156" t="inlineStr">
+        <is>
+          <t>Top árbitros de inversor: Alexandrov (20), Fortier (16), Brower (14). Top árbitros de estado: Stern (52), Thomas (17), Douglas (15). Alta concentración en &lt; 20 árbitros.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="160" t="inlineStr">
+        <is>
+          <t>E. IMPACTO ECONÓMICO</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="55" customHeight="1">
+      <c r="A25" s="154" t="inlineStr">
+        <is>
+          <t>C14</t>
+        </is>
+      </c>
+      <c r="B25" s="155" t="inlineStr">
+        <is>
+          <t>Importadores netos pagaron USD 30.302 mill. en condenas (promedio USD 285.9 mill./caso). Exportadores netos: USD 1.979 mill. (promedio USD 61.9 mill./caso). El impacto económico absoluto es 15x mayor sobre importadores.</t>
+        </is>
+      </c>
+      <c r="C25" s="156" t="inlineStr">
+        <is>
+          <t>Condena más alta sobre importador: ConocoPhillips v. Venezuela (USD 8.366 mill.). Más alta sobre exportador: NextEra v. Spain (USD 323.6 mill.). Total global con datos: USD 32.378 mill.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="55" customHeight="1">
+      <c r="A26" s="154" t="inlineStr">
+        <is>
+          <t>C15</t>
+        </is>
+      </c>
+      <c r="B26" s="155" t="inlineStr">
+        <is>
+          <t>Las anulaciones modifican el resultado final en pocos casos: solo 5 laudos anulados totalmente y 10 parcialmente de 174 procesos de anulación iniciados. El sistema tiende a confirmar los laudos originales (94 confirmados de los resueltos).</t>
+        </is>
+      </c>
+      <c r="C26" s="156" t="inlineStr">
+        <is>
+          <t>Anulados total: 5. Anulados parcial: 10. Confirmados: 94. Pendientes: 36. Los estados que apelan rara vez logran la anulación total.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="161" t="inlineStr">
+        <is>
+          <t>F. LIMITACIONES</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="55" customHeight="1">
+      <c r="A29" s="154" t="inlineStr">
+        <is>
+          <t>C16</t>
+        </is>
+      </c>
+      <c r="B29" s="155" t="inlineStr">
+        <is>
+          <t>29 casos tienen laudo confidencial (sin acceso público): 14 son absoluciones del estado, 9 son condenas con daños, 2 son condenas sin daños. No hay sesgo grosero pero la muestra no es del 100% del universo.</t>
+        </is>
+      </c>
+      <c r="C29" s="156" t="inlineStr">
+        <is>
+          <t>19 de los 29 son importadores netos, 6 exportadores. Las condenas con daños confidenciales representan el 5.5% del total de condenas con daños. Limitación metodológica a declarar en la tesis.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A24:C24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="58" t="inlineStr">
+        <is>
+          <t>DISTRIBUCIÓN DE RESULTADOS EN LAUDOS CIADI 2000-2022 — Por clasificación de flujos de capital (BM)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="78" t="inlineStr">
+        <is>
+          <t>Clasificación</t>
+        </is>
+      </c>
+      <c r="B2" s="78" t="inlineStr">
+        <is>
+          <t>⬛ TOTAL
+de casos</t>
+        </is>
+      </c>
+      <c r="C2" s="110" t="n"/>
+      <c r="D2" s="79" t="inlineStr">
+        <is>
+          <t>🔴 Condena
+con daños</t>
+        </is>
+      </c>
+      <c r="E2" s="110" t="n"/>
+      <c r="F2" s="80" t="inlineStr">
+        <is>
+          <t>🟡 Condena
+sin daños</t>
+        </is>
+      </c>
+      <c r="G2" s="110" t="n"/>
+      <c r="H2" s="81" t="inlineStr">
+        <is>
+          <t>🟢 Estado
+absuelto</t>
+        </is>
+      </c>
+      <c r="I2" s="110" t="n"/>
+      <c r="J2" s="82" t="inlineStr">
+        <is>
+          <t>🔴+🟡 TOTAL
+condenas</t>
+        </is>
+      </c>
+      <c r="K2" s="110" t="n"/>
+    </row>
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="111" t="n"/>
+      <c r="B3" s="83" t="inlineStr">
+        <is>
+          <t>N°</t>
+        </is>
+      </c>
+      <c r="C3" s="83" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D3" s="84" t="inlineStr">
+        <is>
+          <t>N°</t>
+        </is>
+      </c>
+      <c r="E3" s="84" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="F3" s="85" t="inlineStr">
+        <is>
+          <t>N°</t>
+        </is>
+      </c>
+      <c r="G3" s="85" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="H3" s="86" t="inlineStr">
+        <is>
+          <t>N°</t>
+        </is>
+      </c>
+      <c r="I3" s="86" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="J3" s="87" t="inlineStr">
+        <is>
+          <t>N°</t>
+        </is>
+      </c>
+      <c r="K3" s="87" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="88" t="inlineStr">
+        <is>
+          <t>▸ 1. UNIVERSO TOTAL — 350 laudos con decisión pública (2000-2022)</t>
+        </is>
+      </c>
+      <c r="B4" s="112" t="n"/>
+      <c r="C4" s="112" t="n"/>
+      <c r="D4" s="112" t="n"/>
+      <c r="E4" s="112" t="n"/>
+      <c r="F4" s="112" t="n"/>
+      <c r="G4" s="112" t="n"/>
+      <c r="H4" s="112" t="n"/>
+      <c r="I4" s="112" t="n"/>
+      <c r="J4" s="112" t="n"/>
+      <c r="K4" s="110" t="n"/>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="89" t="inlineStr">
+        <is>
+          <t>TOTAL GLOBAL</t>
+        </is>
+      </c>
+      <c r="B5" s="90" t="n">
+        <v>350</v>
+      </c>
+      <c r="C5" s="91" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="92" t="n">
+        <v>150</v>
+      </c>
+      <c r="E5" s="93" t="n">
+        <v>0.4285714285714285</v>
+      </c>
+      <c r="F5" s="94" t="n">
+        <v>14</v>
+      </c>
+      <c r="G5" s="95" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H5" s="96" t="n">
+        <v>186</v>
+      </c>
+      <c r="I5" s="97" t="n">
+        <v>0.5314285714285715</v>
+      </c>
+      <c r="J5" s="87" t="n">
+        <v>164</v>
+      </c>
+      <c r="K5" s="98" t="n">
+        <v>0.4685714285714286</v>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="88" t="inlineStr">
+        <is>
+          <t>▸ 2. POR CLASIFICACIÓN DEL ESTADO DEMANDADO (flujos de IED netos 2000-2022, Banco Mundial)</t>
+        </is>
+      </c>
+      <c r="B7" s="112" t="n"/>
+      <c r="C7" s="112" t="n"/>
+      <c r="D7" s="112" t="n"/>
+      <c r="E7" s="112" t="n"/>
+      <c r="F7" s="112" t="n"/>
+      <c r="G7" s="112" t="n"/>
+      <c r="H7" s="112" t="n"/>
+      <c r="I7" s="112" t="n"/>
+      <c r="J7" s="112" t="n"/>
+      <c r="K7" s="110" t="n"/>
+    </row>
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Exportador neto</t>
+        </is>
+      </c>
+      <c r="B8" s="90" t="n">
+        <v>60</v>
+      </c>
+      <c r="C8" s="91" t="n">
+        <v>0.1714285714285714</v>
+      </c>
+      <c r="D8" s="92" t="n">
+        <v>33</v>
+      </c>
+      <c r="E8" s="93" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F8" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="96" t="n">
+        <v>27</v>
+      </c>
+      <c r="I8" s="97" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J8" s="87" t="n">
+        <v>33</v>
+      </c>
+      <c r="K8" s="98" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
+      <c r="A9" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Importador neto</t>
+        </is>
+      </c>
+      <c r="B9" s="90" t="n">
+        <v>283</v>
+      </c>
+      <c r="C9" s="91" t="n">
+        <v>0.8085714285714286</v>
+      </c>
+      <c r="D9" s="92" t="n">
+        <v>115</v>
+      </c>
+      <c r="E9" s="93" t="n">
+        <v>0.4063604240282686</v>
+      </c>
+      <c r="F9" s="94" t="n">
+        <v>14</v>
+      </c>
+      <c r="G9" s="95" t="n">
+        <v>0.04946996466431095</v>
+      </c>
+      <c r="H9" s="96" t="n">
+        <v>154</v>
+      </c>
+      <c r="I9" s="97" t="n">
+        <v>0.5441696113074205</v>
+      </c>
+      <c r="J9" s="87" t="n">
+        <v>129</v>
+      </c>
+      <c r="K9" s="98" t="n">
+        <v>0.4558303886925795</v>
+      </c>
+    </row>
+    <row r="10" ht="16" customHeight="1">
+      <c r="A10" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      → Top estados exportadores demandados:</t>
+        </is>
+      </c>
+      <c r="B10" s="102" t="inlineStr"/>
+      <c r="C10" s="102" t="inlineStr"/>
+      <c r="D10" s="102" t="inlineStr"/>
+      <c r="E10" s="102" t="inlineStr"/>
+      <c r="F10" s="102" t="inlineStr"/>
+      <c r="G10" s="102" t="inlineStr"/>
+      <c r="H10" s="102" t="inlineStr"/>
+      <c r="I10" s="102" t="inlineStr"/>
+      <c r="J10" s="102" t="inlineStr"/>
+      <c r="K10" s="102" t="inlineStr"/>
+    </row>
+    <row r="11" ht="16" customHeight="1">
+      <c r="A11" s="103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Spain ⚠️ ECT</t>
+        </is>
+      </c>
+      <c r="B11" s="102" t="n">
+        <v>25</v>
+      </c>
+      <c r="C11" s="104" t="n">
+        <v>0.07142857142857142</v>
+      </c>
+      <c r="D11" s="92" t="n">
+        <v>23</v>
+      </c>
+      <c r="E11" s="93" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="F11" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="96" t="n">
+        <v>2</v>
+      </c>
+      <c r="I11" s="97" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="J11" s="87" t="n">
+        <v>23</v>
+      </c>
+      <c r="K11" s="98" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="12" ht="16" customHeight="1">
+      <c r="A12" s="103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Italy</t>
+        </is>
+      </c>
+      <c r="B12" s="102" t="n">
+        <v>6</v>
+      </c>
+      <c r="C12" s="104" t="n">
+        <v>0.01714285714285714</v>
+      </c>
+      <c r="D12" s="92" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="93" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F12" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="96" t="n">
+        <v>4</v>
+      </c>
+      <c r="I12" s="97" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J12" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="K12" s="98" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="13" ht="16" customHeight="1">
+      <c r="A13" s="103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Serbia</t>
+        </is>
+      </c>
+      <c r="B13" s="102" t="n">
+        <v>6</v>
+      </c>
+      <c r="C13" s="104" t="n">
+        <v>0.01714285714285714</v>
+      </c>
+      <c r="D13" s="92" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="93" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F13" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="96" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="97" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="J13" s="87" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" s="98" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="14" ht="16" customHeight="1">
+      <c r="A14" s="103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Uzbekistan</t>
+        </is>
+      </c>
+      <c r="B14" s="102" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" s="104" t="n">
+        <v>0.008571428571428572</v>
+      </c>
+      <c r="D14" s="92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="93" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F14" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="96" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="97" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J14" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="98" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="15" ht="16" customHeight="1">
+      <c r="A15" s="103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Iraq</t>
+        </is>
+      </c>
+      <c r="B15" s="102" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" s="104" t="n">
+        <v>0.008571428571428572</v>
+      </c>
+      <c r="D15" s="92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="93" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="96" t="n">
+        <v>3</v>
+      </c>
+      <c r="I15" s="97" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" s="87" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      → Top estados importadores demandados:</t>
+        </is>
+      </c>
+      <c r="B16" s="102" t="inlineStr"/>
+      <c r="C16" s="102" t="inlineStr"/>
+      <c r="D16" s="102" t="inlineStr"/>
+      <c r="E16" s="102" t="inlineStr"/>
+      <c r="F16" s="102" t="inlineStr"/>
+      <c r="G16" s="102" t="inlineStr"/>
+      <c r="H16" s="102" t="inlineStr"/>
+      <c r="I16" s="102" t="inlineStr"/>
+      <c r="J16" s="102" t="inlineStr"/>
+      <c r="K16" s="102" t="inlineStr"/>
+    </row>
+    <row r="17" ht="16" customHeight="1">
+      <c r="A17" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Venezuela, Bolivarian Republic of</t>
+        </is>
+      </c>
+      <c r="B17" s="102" t="n">
+        <v>26</v>
+      </c>
+      <c r="C17" s="104" t="n">
+        <v>0.07428571428571429</v>
+      </c>
+      <c r="D17" s="92" t="n">
+        <v>17</v>
+      </c>
+      <c r="E17" s="93" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+      <c r="F17" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="96" t="n">
+        <v>9</v>
+      </c>
+      <c r="I17" s="97" t="n">
+        <v>0.3461538461538461</v>
+      </c>
+      <c r="J17" s="87" t="n">
+        <v>17</v>
+      </c>
+      <c r="K17" s="98" t="n">
+        <v>0.6538461538461539</v>
+      </c>
+    </row>
+    <row r="18" ht="16" customHeight="1">
+      <c r="A18" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Argentina</t>
+        </is>
+      </c>
+      <c r="B18" s="102" t="n">
+        <v>24</v>
+      </c>
+      <c r="C18" s="104" t="n">
+        <v>0.06857142857142857</v>
+      </c>
+      <c r="D18" s="92" t="n">
+        <v>18</v>
+      </c>
+      <c r="E18" s="93" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F18" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="95" t="n">
+        <v>0.04166666666666666</v>
+      </c>
+      <c r="H18" s="96" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" s="97" t="n">
+        <v>0.2083333333333333</v>
+      </c>
+      <c r="J18" s="87" t="n">
+        <v>19</v>
+      </c>
+      <c r="K18" s="98" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+    </row>
+    <row r="19" ht="16" customHeight="1">
+      <c r="A19" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Hungary</t>
+        </is>
+      </c>
+      <c r="B19" s="102" t="n">
+        <v>13</v>
+      </c>
+      <c r="C19" s="104" t="n">
+        <v>0.03714285714285714</v>
+      </c>
+      <c r="D19" s="92" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" s="93" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="F19" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="96" t="n">
+        <v>7</v>
+      </c>
+      <c r="I19" s="97" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="J19" s="87" t="n">
+        <v>6</v>
+      </c>
+      <c r="K19" s="98" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+    </row>
+    <row r="20" ht="16" customHeight="1">
+      <c r="A20" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Egypt</t>
+        </is>
+      </c>
+      <c r="B20" s="102" t="n">
+        <v>13</v>
+      </c>
+      <c r="C20" s="104" t="n">
+        <v>0.03714285714285714</v>
+      </c>
+      <c r="D20" s="92" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="93" t="n">
+        <v>0.1538461538461539</v>
+      </c>
+      <c r="F20" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="95" t="n">
+        <v>0.07692307692307693</v>
+      </c>
+      <c r="H20" s="96" t="n">
+        <v>10</v>
+      </c>
+      <c r="I20" s="97" t="n">
+        <v>0.7692307692307693</v>
+      </c>
+      <c r="J20" s="87" t="n">
+        <v>3</v>
+      </c>
+      <c r="K20" s="98" t="n">
+        <v>0.2307692307692308</v>
+      </c>
+    </row>
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Mexico</t>
+        </is>
+      </c>
+      <c r="B21" s="102" t="n">
+        <v>13</v>
+      </c>
+      <c r="C21" s="104" t="n">
+        <v>0.03714285714285714</v>
+      </c>
+      <c r="D21" s="92" t="n">
+        <v>8</v>
+      </c>
+      <c r="E21" s="93" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+      <c r="F21" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="96" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" s="97" t="n">
+        <v>0.3846153846153846</v>
+      </c>
+      <c r="J21" s="87" t="n">
+        <v>8</v>
+      </c>
+      <c r="K21" s="98" t="n">
+        <v>0.6153846153846154</v>
+      </c>
+    </row>
+    <row r="22" ht="16" customHeight="1">
+      <c r="A22" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Romania</t>
+        </is>
+      </c>
+      <c r="B22" s="102" t="n">
+        <v>11</v>
+      </c>
+      <c r="C22" s="104" t="n">
+        <v>0.03142857142857143</v>
+      </c>
+      <c r="D22" s="92" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="93" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="F22" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="95" t="n">
+        <v>0.09090909090909091</v>
+      </c>
+      <c r="H22" s="96" t="n">
+        <v>7</v>
+      </c>
+      <c r="I22" s="97" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="J22" s="87" t="n">
+        <v>4</v>
+      </c>
+      <c r="K22" s="98" t="n">
+        <v>0.3636363636363636</v>
+      </c>
+    </row>
+    <row r="23" ht="16" customHeight="1">
+      <c r="A23" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Ukraine</t>
+        </is>
+      </c>
+      <c r="B23" s="102" t="n">
+        <v>10</v>
+      </c>
+      <c r="C23" s="104" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="D23" s="92" t="n">
+        <v>4</v>
+      </c>
+      <c r="E23" s="93" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F23" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="96" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" s="97" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J23" s="87" t="n">
+        <v>4</v>
+      </c>
+      <c r="K23" s="98" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Türkiye</t>
+        </is>
+      </c>
+      <c r="B24" s="102" t="n">
+        <v>10</v>
+      </c>
+      <c r="C24" s="104" t="n">
+        <v>0.02857142857142857</v>
+      </c>
+      <c r="D24" s="92" t="n">
+        <v>2</v>
+      </c>
+      <c r="E24" s="93" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F24" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="96" t="n">
+        <v>8</v>
+      </c>
+      <c r="I24" s="97" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J24" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" s="98" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="88" t="inlineStr">
+        <is>
+          <t>▸ 3. POR CLASIFICACIÓN DEL PAÍS INVERSOR (flujos de IED netos 2000-2022, Banco Mundial)</t>
+        </is>
+      </c>
+      <c r="B26" s="112" t="n"/>
+      <c r="C26" s="112" t="n"/>
+      <c r="D26" s="112" t="n"/>
+      <c r="E26" s="112" t="n"/>
+      <c r="F26" s="112" t="n"/>
+      <c r="G26" s="112" t="n"/>
+      <c r="H26" s="112" t="n"/>
+      <c r="I26" s="112" t="n"/>
+      <c r="J26" s="112" t="n"/>
+      <c r="K26" s="110" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1">
+      <c r="A27" s="99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Exportador neto</t>
+        </is>
+      </c>
+      <c r="B27" s="90" t="n">
+        <v>228</v>
+      </c>
+      <c r="C27" s="91" t="n">
+        <v>0.6514285714285715</v>
+      </c>
+      <c r="D27" s="92" t="n">
+        <v>97</v>
+      </c>
+      <c r="E27" s="93" t="n">
+        <v>0.4254385964912281</v>
+      </c>
+      <c r="F27" s="94" t="n">
+        <v>11</v>
+      </c>
+      <c r="G27" s="95" t="n">
+        <v>0.04824561403508772</v>
+      </c>
+      <c r="H27" s="96" t="n">
+        <v>120</v>
+      </c>
+      <c r="I27" s="97" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="J27" s="87" t="n">
+        <v>108</v>
+      </c>
+      <c r="K27" s="98" t="n">
+        <v>0.4736842105263158</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1">
+      <c r="A28" s="100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Importador neto</t>
+        </is>
+      </c>
+      <c r="B28" s="90" t="n">
+        <v>79</v>
+      </c>
+      <c r="C28" s="91" t="n">
+        <v>0.2257142857142857</v>
+      </c>
+      <c r="D28" s="92" t="n">
+        <v>26</v>
+      </c>
+      <c r="E28" s="93" t="n">
+        <v>0.3291139240506329</v>
+      </c>
+      <c r="F28" s="94" t="n">
+        <v>2</v>
+      </c>
+      <c r="G28" s="95" t="n">
+        <v>0.02531645569620253</v>
+      </c>
+      <c r="H28" s="96" t="n">
+        <v>51</v>
+      </c>
+      <c r="I28" s="97" t="n">
+        <v>0.6455696202531646</v>
+      </c>
+      <c r="J28" s="87" t="n">
+        <v>28</v>
+      </c>
+      <c r="K28" s="98" t="n">
+        <v>0.3544303797468354</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      → Top países inversores exportadores:</t>
+        </is>
+      </c>
+      <c r="B29" s="102" t="inlineStr"/>
+      <c r="C29" s="102" t="inlineStr"/>
+      <c r="D29" s="102" t="inlineStr"/>
+      <c r="E29" s="102" t="inlineStr"/>
+      <c r="F29" s="102" t="inlineStr"/>
+      <c r="G29" s="102" t="inlineStr"/>
+      <c r="H29" s="102" t="inlineStr"/>
+      <c r="I29" s="102" t="inlineStr"/>
+      <c r="J29" s="102" t="inlineStr"/>
+      <c r="K29" s="102" t="inlineStr"/>
+    </row>
+    <row r="30" ht="16" customHeight="1">
+      <c r="A30" s="103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        United States of America</t>
+        </is>
+      </c>
+      <c r="B30" s="102" t="n">
+        <v>62</v>
+      </c>
+      <c r="C30" s="104" t="n">
+        <v>0.1771428571428571</v>
+      </c>
+      <c r="D30" s="92" t="n">
+        <v>23</v>
+      </c>
+      <c r="E30" s="93" t="n">
+        <v>0.3709677419354839</v>
+      </c>
+      <c r="F30" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="96" t="n">
+        <v>39</v>
+      </c>
+      <c r="I30" s="97" t="n">
+        <v>0.6290322580645161</v>
+      </c>
+      <c r="J30" s="87" t="n">
+        <v>23</v>
+      </c>
+      <c r="K30" s="98" t="n">
+        <v>0.3709677419354839</v>
+      </c>
+    </row>
+    <row r="31" ht="16" customHeight="1">
+      <c r="A31" s="103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Netherlands</t>
+        </is>
+      </c>
+      <c r="B31" s="102" t="n">
+        <v>28</v>
+      </c>
+      <c r="C31" s="104" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D31" s="92" t="n">
+        <v>9</v>
+      </c>
+      <c r="E31" s="93" t="n">
+        <v>0.3214285714285715</v>
+      </c>
+      <c r="F31" s="94" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" s="95" t="n">
+        <v>0.1428571428571428</v>
+      </c>
+      <c r="H31" s="96" t="n">
+        <v>15</v>
+      </c>
+      <c r="I31" s="97" t="n">
+        <v>0.5357142857142857</v>
+      </c>
+      <c r="J31" s="87" t="n">
+        <v>13</v>
+      </c>
+      <c r="K31" s="98" t="n">
+        <v>0.4642857142857143</v>
+      </c>
+    </row>
+    <row r="32" ht="16" customHeight="1">
+      <c r="A32" s="103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Germany</t>
+        </is>
+      </c>
+      <c r="B32" s="102" t="n">
+        <v>24</v>
+      </c>
+      <c r="C32" s="104" t="n">
+        <v>0.06857142857142857</v>
+      </c>
+      <c r="D32" s="92" t="n">
+        <v>13</v>
+      </c>
+      <c r="E32" s="93" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="F32" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="96" t="n">
+        <v>11</v>
+      </c>
+      <c r="I32" s="97" t="n">
+        <v>0.4583333333333333</v>
+      </c>
+      <c r="J32" s="87" t="n">
+        <v>13</v>
+      </c>
+      <c r="K32" s="98" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+    </row>
+    <row r="33" ht="16" customHeight="1">
+      <c r="A33" s="103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Spain</t>
+        </is>
+      </c>
+      <c r="B33" s="102" t="n">
+        <v>19</v>
+      </c>
+      <c r="C33" s="104" t="n">
+        <v>0.05428571428571428</v>
+      </c>
+      <c r="D33" s="92" t="n">
+        <v>7</v>
+      </c>
+      <c r="E33" s="93" t="n">
+        <v>0.3684210526315789</v>
+      </c>
+      <c r="F33" s="94" t="n">
+        <v>3</v>
+      </c>
+      <c r="G33" s="95" t="n">
+        <v>0.1578947368421053</v>
+      </c>
+      <c r="H33" s="96" t="n">
+        <v>9</v>
+      </c>
+      <c r="I33" s="97" t="n">
+        <v>0.4736842105263158</v>
+      </c>
+      <c r="J33" s="87" t="n">
+        <v>10</v>
+      </c>
+      <c r="K33" s="98" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+    </row>
+    <row r="34" ht="16" customHeight="1">
+      <c r="A34" s="103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        France</t>
+        </is>
+      </c>
+      <c r="B34" s="102" t="n">
+        <v>15</v>
+      </c>
+      <c r="C34" s="104" t="n">
+        <v>0.04285714285714286</v>
+      </c>
+      <c r="D34" s="92" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" s="93" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="F34" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="96" t="n">
+        <v>5</v>
+      </c>
+      <c r="I34" s="97" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="J34" s="87" t="n">
+        <v>10</v>
+      </c>
+      <c r="K34" s="98" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+    </row>
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Italy</t>
+        </is>
+      </c>
+      <c r="B35" s="102" t="n">
+        <v>15</v>
+      </c>
+      <c r="C35" s="104" t="n">
+        <v>0.04285714285714286</v>
+      </c>
+      <c r="D35" s="92" t="n">
+        <v>6</v>
+      </c>
+      <c r="E35" s="93" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F35" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="96" t="n">
+        <v>9</v>
+      </c>
+      <c r="I35" s="97" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J35" s="87" t="n">
+        <v>6</v>
+      </c>
+      <c r="K35" s="98" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      → Top países inversores importadores:</t>
+        </is>
+      </c>
+      <c r="B36" s="102" t="inlineStr"/>
+      <c r="C36" s="102" t="inlineStr"/>
+      <c r="D36" s="102" t="inlineStr"/>
+      <c r="E36" s="102" t="inlineStr"/>
+      <c r="F36" s="102" t="inlineStr"/>
+      <c r="G36" s="102" t="inlineStr"/>
+      <c r="H36" s="102" t="inlineStr"/>
+      <c r="I36" s="102" t="inlineStr"/>
+      <c r="J36" s="102" t="inlineStr"/>
+      <c r="K36" s="102" t="inlineStr"/>
+    </row>
+    <row r="37" ht="16" customHeight="1">
+      <c r="A37" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        United Kingdom</t>
+        </is>
+      </c>
+      <c r="B37" s="102" t="n">
+        <v>22</v>
+      </c>
+      <c r="C37" s="104" t="n">
+        <v>0.06285714285714286</v>
+      </c>
+      <c r="D37" s="92" t="n">
+        <v>6</v>
+      </c>
+      <c r="E37" s="93" t="n">
+        <v>0.2727272727272727</v>
+      </c>
+      <c r="F37" s="94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="95" t="n">
+        <v>0.04545454545454546</v>
+      </c>
+      <c r="H37" s="96" t="n">
+        <v>15</v>
+      </c>
+      <c r="I37" s="97" t="n">
+        <v>0.6818181818181818</v>
+      </c>
+      <c r="J37" s="87" t="n">
+        <v>7</v>
+      </c>
+      <c r="K37" s="98" t="n">
+        <v>0.3181818181818182</v>
+      </c>
+    </row>
+    <row r="38" ht="16" customHeight="1">
+      <c r="A38" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Türkiye</t>
+        </is>
+      </c>
+      <c r="B38" s="102" t="n">
+        <v>13</v>
+      </c>
+      <c r="C38" s="104" t="n">
+        <v>0.03714285714285714</v>
+      </c>
+      <c r="D38" s="92" t="n">
+        <v>7</v>
+      </c>
+      <c r="E38" s="93" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+      <c r="F38" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="96" t="n">
+        <v>6</v>
+      </c>
+      <c r="I38" s="97" t="n">
+        <v>0.4615384615384616</v>
+      </c>
+      <c r="J38" s="87" t="n">
+        <v>7</v>
+      </c>
+      <c r="K38" s="98" t="n">
+        <v>0.5384615384615384</v>
+      </c>
+    </row>
+    <row r="39" ht="16" customHeight="1">
+      <c r="A39" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Greece</t>
+        </is>
+      </c>
+      <c r="B39" s="102" t="n">
+        <v>5</v>
+      </c>
+      <c r="C39" s="104" t="n">
+        <v>0.01428571428571429</v>
+      </c>
+      <c r="D39" s="92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" s="93" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F39" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="96" t="n">
+        <v>4</v>
+      </c>
+      <c r="I39" s="97" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J39" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" s="98" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="40" ht="16" customHeight="1">
+      <c r="A40" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Lithuania</t>
+        </is>
+      </c>
+      <c r="B40" s="102" t="n">
+        <v>4</v>
+      </c>
+      <c r="C40" s="104" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="D40" s="92" t="n">
+        <v>2</v>
+      </c>
+      <c r="E40" s="93" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F40" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="96" t="n">
+        <v>2</v>
+      </c>
+      <c r="I40" s="97" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J40" s="87" t="n">
+        <v>2</v>
+      </c>
+      <c r="K40" s="98" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="41" ht="16" customHeight="1">
+      <c r="A41" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        Barbados</t>
+        </is>
+      </c>
+      <c r="B41" s="102" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" s="104" t="n">
+        <v>0.01142857142857143</v>
+      </c>
+      <c r="D41" s="92" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" s="93" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F41" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="96" t="n">
+        <v>3</v>
+      </c>
+      <c r="I41" s="97" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J41" s="87" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" s="98" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="88" t="inlineStr">
+        <is>
+          <t>▸ 4. TABLA CRUZADA — Estado demandado × País inversor (solo exportador/importador)</t>
+        </is>
+      </c>
+      <c r="B43" s="112" t="n"/>
+      <c r="C43" s="112" t="n"/>
+      <c r="D43" s="112" t="n"/>
+      <c r="E43" s="112" t="n"/>
+      <c r="F43" s="112" t="n"/>
+      <c r="G43" s="112" t="n"/>
+      <c r="H43" s="112" t="n"/>
+      <c r="I43" s="112" t="n"/>
+      <c r="J43" s="112" t="n"/>
+      <c r="K43" s="110" t="n"/>
+    </row>
+    <row r="44" ht="18" customHeight="1">
+      <c r="A44" s="103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Estado Exportador neto ← Inversor Exportador neto</t>
+        </is>
+      </c>
+      <c r="B44" s="102" t="n">
+        <v>28</v>
+      </c>
+      <c r="C44" s="104" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="D44" s="92" t="n">
+        <v>14</v>
+      </c>
+      <c r="E44" s="93" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F44" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="96" t="n">
+        <v>14</v>
+      </c>
+      <c r="I44" s="97" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J44" s="87" t="n">
+        <v>14</v>
+      </c>
+      <c r="K44" s="98" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1">
+      <c r="A45" s="103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Estado Exportador neto ← Inversor Importador neto</t>
+        </is>
+      </c>
+      <c r="B45" s="102" t="n">
+        <v>15</v>
+      </c>
+      <c r="C45" s="104" t="n">
+        <v>0.04285714285714286</v>
+      </c>
+      <c r="D45" s="92" t="n">
+        <v>5</v>
+      </c>
+      <c r="E45" s="93" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F45" s="94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="96" t="n">
+        <v>10</v>
+      </c>
+      <c r="I45" s="97" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="J45" s="87" t="n">
+        <v>5</v>
+      </c>
+      <c r="K45" s="98" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1">
+      <c r="A46" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Estado Importador neto ← Inversor Exportador neto</t>
+        </is>
+      </c>
+      <c r="B46" s="102" t="n">
+        <v>194</v>
+      </c>
+      <c r="C46" s="104" t="n">
+        <v>0.5542857142857143</v>
+      </c>
+      <c r="D46" s="92" t="n">
+        <v>81</v>
+      </c>
+      <c r="E46" s="93" t="n">
+        <v>0.4175257731958763</v>
+      </c>
+      <c r="F46" s="94" t="n">
+        <v>11</v>
+      </c>
+      <c r="G46" s="95" t="n">
+        <v>0.05670103092783505</v>
+      </c>
+      <c r="H46" s="96" t="n">
+        <v>102</v>
+      </c>
+      <c r="I46" s="97" t="n">
+        <v>0.5257731958762887</v>
+      </c>
+      <c r="J46" s="87" t="n">
+        <v>92</v>
+      </c>
+      <c r="K46" s="98" t="n">
+        <v>0.4742268041237113</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1">
+      <c r="A47" s="105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Estado Importador neto ← Inversor Importador neto</t>
+        </is>
+      </c>
+      <c r="B47" s="102" t="n">
+        <v>63</v>
+      </c>
+      <c r="C47" s="104" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="D47" s="92" t="n">
+        <v>21</v>
+      </c>
+      <c r="E47" s="93" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F47" s="94" t="n">
+        <v>2</v>
+      </c>
+      <c r="G47" s="95" t="n">
+        <v>0.03174603174603174</v>
+      </c>
+      <c r="H47" s="96" t="n">
+        <v>40</v>
+      </c>
+      <c r="I47" s="97" t="n">
+        <v>0.6349206349206349</v>
+      </c>
+      <c r="J47" s="87" t="n">
+        <v>23</v>
+      </c>
+      <c r="K47" s="98" t="n">
+        <v>0.3650793650793651</v>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1">
+      <c r="A49" s="106" t="inlineStr">
+        <is>
+          <t>▸ NOTAS METODOLÓGICAS</t>
+        </is>
+      </c>
+      <c r="B49" s="112" t="n"/>
+      <c r="C49" s="112" t="n"/>
+      <c r="D49" s="112" t="n"/>
+      <c r="E49" s="112" t="n"/>
+      <c r="F49" s="112" t="n"/>
+      <c r="G49" s="112" t="n"/>
+      <c r="H49" s="112" t="n"/>
+      <c r="I49" s="112" t="n"/>
+      <c r="J49" s="112" t="n"/>
+      <c r="K49" s="110" t="n"/>
+    </row>
+    <row r="50" ht="22" customHeight="1">
+      <c r="A50" s="107" t="inlineStr">
+        <is>
+          <t>• Universo: 350 laudos con decisión pública del CIADI (2000-2022). No incluye casos discontinuados, arreglos amistosos ni laudos confidenciales (aprox. 29 casos sin acceso público).</t>
+        </is>
+      </c>
+      <c r="B50" s="112" t="n"/>
+      <c r="C50" s="112" t="n"/>
+      <c r="D50" s="112" t="n"/>
+      <c r="E50" s="112" t="n"/>
+      <c r="F50" s="112" t="n"/>
+      <c r="G50" s="112" t="n"/>
+      <c r="H50" s="112" t="n"/>
+      <c r="I50" s="112" t="n"/>
+      <c r="J50" s="112" t="n"/>
+      <c r="K50" s="110" t="n"/>
+    </row>
+    <row r="51" ht="22" customHeight="1">
+      <c r="A51" s="107" t="inlineStr">
+        <is>
+          <t>• Clasificación de flujos: (Σ salidas IED − Σ entradas IED) / 23 años. Positivo = exportador neto. Fuente: Banco Mundial (BX.KLT.DINV / BM.KLT.DINV), 2000-2022.</t>
+        </is>
+      </c>
+      <c r="B51" s="112" t="n"/>
+      <c r="C51" s="112" t="n"/>
+      <c r="D51" s="112" t="n"/>
+      <c r="E51" s="112" t="n"/>
+      <c r="F51" s="112" t="n"/>
+      <c r="G51" s="112" t="n"/>
+      <c r="H51" s="112" t="n"/>
+      <c r="I51" s="112" t="n"/>
+      <c r="J51" s="112" t="n"/>
+      <c r="K51" s="110" t="n"/>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="107" t="inlineStr">
+        <is>
+          <t>• España clasificada como exportadora neta por BM (neto +USD 12,616 mill./año). Sus 25 casos (23 condenas) corresponden al ECT/renovables 2013-2016. Verificar con UNCTAD.</t>
+        </is>
+      </c>
+      <c r="B52" s="112" t="n"/>
+      <c r="C52" s="112" t="n"/>
+      <c r="D52" s="112" t="n"/>
+      <c r="E52" s="112" t="n"/>
+      <c r="F52" s="112" t="n"/>
+      <c r="G52" s="112" t="n"/>
+      <c r="H52" s="112" t="n"/>
+      <c r="I52" s="112" t="n"/>
+      <c r="J52" s="112" t="n"/>
+      <c r="K52" s="110" t="n"/>
+    </row>
+    <row r="53" ht="22" customHeight="1">
+      <c r="A53" s="107" t="inlineStr">
+        <is>
+          <t>• "Condena sin daños" = arbitros reconocieron violación del TBI pero no otorgaron compensación monetaria (ej. solo costas, o daño ya compensado por otro medio).</t>
+        </is>
+      </c>
+      <c r="B53" s="112" t="n"/>
+      <c r="C53" s="112" t="n"/>
+      <c r="D53" s="112" t="n"/>
+      <c r="E53" s="112" t="n"/>
+      <c r="F53" s="112" t="n"/>
+      <c r="G53" s="112" t="n"/>
+      <c r="H53" s="112" t="n"/>
+      <c r="I53" s="112" t="n"/>
+      <c r="J53" s="112" t="n"/>
+      <c r="K53" s="110" t="n"/>
+    </row>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="107" t="inlineStr">
+        <is>
+          <t>• Los 7 casos "Sin datos" de clasificación corresponden a países sin información suficiente en el Banco Mundial.</t>
+        </is>
+      </c>
+      <c r="B54" s="112" t="n"/>
+      <c r="C54" s="112" t="n"/>
+      <c r="D54" s="112" t="n"/>
+      <c r="E54" s="112" t="n"/>
+      <c r="F54" s="112" t="n"/>
+      <c r="G54" s="112" t="n"/>
+      <c r="H54" s="112" t="n"/>
+      <c r="I54" s="112" t="n"/>
+      <c r="J54" s="112" t="n"/>
+      <c r="K54" s="110" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="A53:K53"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="A50:K50"/>
+    <mergeCell ref="A54:K54"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="A7:K7"/>
+    <mergeCell ref="A43:K43"/>
+    <mergeCell ref="A49:K49"/>
+    <mergeCell ref="A51:K51"/>
+    <mergeCell ref="A52:K52"/>
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J95"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="113" t="inlineStr">
+        <is>
+          <t>▸ ANÁLISIS DE MONTOS OTORGADOS Y ÁRBITROS — CIADI 2000-2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="114" t="inlineStr">
+        <is>
+          <t>1. MONTOS OTORGADOS (USD mill.) POR CLASIFICACIÓN DEL ESTADO DEMANDADO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="115" t="inlineStr"/>
+      <c r="B4" s="115" t="inlineStr">
+        <is>
+          <t>N° condenas</t>
+        </is>
+      </c>
+      <c r="C4" s="115" t="inlineStr">
+        <is>
+          <t>Con monto disp.</t>
+        </is>
+      </c>
+      <c r="D4" s="115" t="inlineStr">
+        <is>
+          <t>TOTAL USD mill.</t>
+        </is>
+      </c>
+      <c r="E4" s="115" t="inlineStr">
+        <is>
+          <t>Promedio/caso</t>
+        </is>
+      </c>
+      <c r="F4" s="115" t="inlineStr">
+        <is>
+          <t>Mediana</t>
+        </is>
+      </c>
+      <c r="G4" s="115" t="inlineStr">
+        <is>
+          <t>Máximo</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="116" t="inlineStr">
+        <is>
+          <t>Exportador neto</t>
+        </is>
+      </c>
+      <c r="B5" s="117" t="n">
+        <v>33</v>
+      </c>
+      <c r="C5" s="117" t="n">
+        <v>32</v>
+      </c>
+      <c r="D5" s="118" t="n">
+        <v>1979.3</v>
+      </c>
+      <c r="E5" s="118" t="n">
+        <v>61.85312500000001</v>
+      </c>
+      <c r="F5" s="118" t="n">
+        <v>34.59999999999999</v>
+      </c>
+      <c r="G5" s="118" t="n">
+        <v>323.6</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="119" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="B6" s="120" t="n">
+        <v>131</v>
+      </c>
+      <c r="C6" s="120" t="n">
+        <v>112</v>
+      </c>
+      <c r="D6" s="121" t="n">
+        <v>30398.75</v>
+      </c>
+      <c r="E6" s="121" t="n">
+        <v>271.4174107142857</v>
+      </c>
+      <c r="F6" s="121" t="n">
+        <v>40.09999999999999</v>
+      </c>
+      <c r="G6" s="121" t="n">
+        <v>8366.1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="122" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="B7" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="123" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="125" t="inlineStr">
+        <is>
+          <t>TOTAL GLOBAL</t>
+        </is>
+      </c>
+      <c r="B8" s="126" t="n">
+        <v>164</v>
+      </c>
+      <c r="C8" s="126" t="n">
+        <v>144</v>
+      </c>
+      <c r="D8" s="127" t="n">
+        <v>32378.05</v>
+      </c>
+      <c r="E8" s="127" t="n">
+        <v>224.8475694444445</v>
+      </c>
+      <c r="F8" s="127" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="G8" s="127" t="n">
+        <v>8366.1</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="114" t="inlineStr">
+        <is>
+          <t>2. TOP 15 CONDENAS MÁS ALTAS (USD mill.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="115" t="inlineStr">
+        <is>
+          <t>Caso</t>
+        </is>
+      </c>
+      <c r="B11" s="115" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="C11" s="115" t="inlineStr">
+        <is>
+          <t>Clasificación</t>
+        </is>
+      </c>
+      <c r="D11" s="115" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+      <c r="E11" s="115" t="inlineStr">
+        <is>
+          <t>USD mill.</t>
+        </is>
+      </c>
+      <c r="F11" s="115" t="inlineStr">
+        <is>
+          <t>ECT?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="128" t="inlineStr">
+        <is>
+          <t>ConocoPhillips v. Venezuela</t>
+        </is>
+      </c>
+      <c r="B12" s="128" t="inlineStr">
+        <is>
+          <t>Venezuela, Bolivarian Republic of</t>
+        </is>
+      </c>
+      <c r="C12" s="120" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D12" s="120" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E12" s="129" t="n">
+        <v>8366.1</v>
+      </c>
+      <c r="F12" s="120" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="128" t="inlineStr">
+        <is>
+          <t>Tethyan Copper v. Pakistan</t>
+        </is>
+      </c>
+      <c r="B13" s="128" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="C13" s="120" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D13" s="120" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E13" s="129" t="n">
+        <v>4087</v>
+      </c>
+      <c r="F13" s="120" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="128" t="inlineStr">
+        <is>
+          <t>Unión Fenosa v. Egypt</t>
+        </is>
+      </c>
+      <c r="B14" s="128" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="C14" s="120" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D14" s="120" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E14" s="129" t="n">
+        <v>2013.1</v>
+      </c>
+      <c r="F14" s="120" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="128" t="inlineStr">
+        <is>
+          <t>Occidental v. Ecuador (II)</t>
+        </is>
+      </c>
+      <c r="B15" s="128" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="C15" s="120" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D15" s="120" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E15" s="129" t="n">
+        <v>1769</v>
+      </c>
+      <c r="F15" s="120" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="128" t="inlineStr">
+        <is>
+          <t>Agroinsumos Ibero-Americanos and others v. Ve</t>
+        </is>
+      </c>
+      <c r="B16" s="128" t="inlineStr">
+        <is>
+          <t>Venezuela, Bolivarian Republic of</t>
+        </is>
+      </c>
+      <c r="C16" s="120" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D16" s="120" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E16" s="129" t="n">
+        <v>1630</v>
+      </c>
+      <c r="F16" s="120" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="128" t="inlineStr">
+        <is>
+          <t>Mobil and others v. Venezuela</t>
+        </is>
+      </c>
+      <c r="B17" s="128" t="inlineStr">
+        <is>
+          <t>Venezuela, Bolivarian Republic of</t>
+        </is>
+      </c>
+      <c r="C17" s="120" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D17" s="120" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E17" s="129" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F17" s="120" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="128" t="inlineStr">
+        <is>
+          <t>Crystallex v. Venezuela</t>
+        </is>
+      </c>
+      <c r="B18" s="128" t="inlineStr">
+        <is>
+          <t>Venezuela, Bolivarian Republic of</t>
+        </is>
+      </c>
+      <c r="C18" s="120" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D18" s="120" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E18" s="129" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F18" s="120" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="128" t="inlineStr">
+        <is>
+          <t>Rusoro Mining v. Venezuela</t>
+        </is>
+      </c>
+      <c r="B19" s="128" t="inlineStr">
+        <is>
+          <t>Venezuela, Bolivarian Republic of</t>
+        </is>
+      </c>
+      <c r="C19" s="120" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D19" s="120" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E19" s="129" t="n">
+        <v>967.8</v>
+      </c>
+      <c r="F19" s="120" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="128" t="inlineStr">
+        <is>
+          <t>Gold Reserve v. Venezuela</t>
+        </is>
+      </c>
+      <c r="B20" s="128" t="inlineStr">
+        <is>
+          <t>Venezuela, Bolivarian Republic of</t>
+        </is>
+      </c>
+      <c r="C20" s="120" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D20" s="120" t="n">
+        <v>2009</v>
+      </c>
+      <c r="E20" s="129" t="n">
+        <v>713</v>
+      </c>
+      <c r="F20" s="120" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="128" t="inlineStr">
+        <is>
+          <t>Karkey Karadeniz v. Pakistan</t>
+        </is>
+      </c>
+      <c r="B21" s="128" t="inlineStr">
+        <is>
+          <t>Pakistan</t>
+        </is>
+      </c>
+      <c r="C21" s="120" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D21" s="120" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E21" s="129" t="n">
+        <v>490.4</v>
+      </c>
+      <c r="F21" s="120" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="128" t="inlineStr">
+        <is>
+          <t>Valores Mundiales and Consorcio Andino v. Ven</t>
+        </is>
+      </c>
+      <c r="B22" s="128" t="inlineStr">
+        <is>
+          <t>Venezuela, Bolivarian Republic of</t>
+        </is>
+      </c>
+      <c r="C22" s="120" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D22" s="120" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E22" s="129" t="n">
+        <v>430.4</v>
+      </c>
+      <c r="F22" s="120" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="128" t="inlineStr">
+        <is>
+          <t>Perenco v. Ecuador</t>
+        </is>
+      </c>
+      <c r="B23" s="128" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="C23" s="120" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D23" s="120" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E23" s="129" t="n">
+        <v>416.5</v>
+      </c>
+      <c r="F23" s="120" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="128" t="inlineStr">
+        <is>
+          <t>Suez and Vivendi v. Argentina (II)</t>
+        </is>
+      </c>
+      <c r="B24" s="128" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="C24" s="120" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D24" s="120" t="n">
+        <v>2003</v>
+      </c>
+      <c r="E24" s="129" t="n">
+        <v>383.6</v>
+      </c>
+      <c r="F24" s="120" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="128" t="inlineStr">
+        <is>
+          <t>Burlington v. Ecuador</t>
+        </is>
+      </c>
+      <c r="B25" s="128" t="inlineStr">
+        <is>
+          <t>Ecuador</t>
+        </is>
+      </c>
+      <c r="C25" s="120" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D25" s="120" t="n">
+        <v>2008</v>
+      </c>
+      <c r="E25" s="129" t="n">
+        <v>379.8</v>
+      </c>
+      <c r="F25" s="120" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="128" t="inlineStr">
+        <is>
+          <t>OIEG v. Venezuela</t>
+        </is>
+      </c>
+      <c r="B26" s="128" t="inlineStr">
+        <is>
+          <t>Venezuela, Bolivarian Republic of</t>
+        </is>
+      </c>
+      <c r="C26" s="120" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D26" s="120" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E26" s="129" t="n">
+        <v>372.4</v>
+      </c>
+      <c r="F26" s="120" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="114" t="inlineStr">
+        <is>
+          <t>3. ANÁLISIS ECT vs NO-ECT — IMPACTO DEL ENERGY CHARTER TREATY</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="115" t="inlineStr">
+        <is>
+          <t>Grupo</t>
+        </is>
+      </c>
+      <c r="B30" s="115" t="inlineStr">
+        <is>
+          <t>Total casos</t>
+        </is>
+      </c>
+      <c r="C30" s="115" t="inlineStr">
+        <is>
+          <t>Cond. c/daños</t>
+        </is>
+      </c>
+      <c r="D30" s="115" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E30" s="115" t="inlineStr">
+        <is>
+          <t>Cond. s/daños</t>
+        </is>
+      </c>
+      <c r="F30" s="115" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="G30" s="115" t="inlineStr">
+        <is>
+          <t>Estado abs.</t>
+        </is>
+      </c>
+      <c r="H30" s="115" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="I30" s="115" t="inlineStr">
+        <is>
+          <t>Total condena</t>
+        </is>
+      </c>
+      <c r="J30" s="115" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="130" t="inlineStr">
+        <is>
+          <t>CON ECT (44 casos)</t>
+        </is>
+      </c>
+      <c r="B31" s="131" t="n">
+        <v>51</v>
+      </c>
+      <c r="C31" s="131" t="n">
+        <v>29</v>
+      </c>
+      <c r="D31" s="132" t="n">
+        <v>0.5686274509803921</v>
+      </c>
+      <c r="E31" s="131" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="132" t="n">
+        <v>0.0392156862745098</v>
+      </c>
+      <c r="G31" s="131" t="n">
+        <v>20</v>
+      </c>
+      <c r="H31" s="132" t="n">
+        <v>0.392156862745098</v>
+      </c>
+      <c r="I31" s="131" t="n">
+        <v>31</v>
+      </c>
+      <c r="J31" s="132" t="n">
+        <v>0.6078431372549019</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="122" t="inlineStr">
+        <is>
+          <t>SIN ECT (299 casos)</t>
+        </is>
+      </c>
+      <c r="B32" s="123" t="n">
+        <v>299</v>
+      </c>
+      <c r="C32" s="123" t="n">
+        <v>121</v>
+      </c>
+      <c r="D32" s="133" t="n">
+        <v>0.4046822742474916</v>
+      </c>
+      <c r="E32" s="123" t="n">
+        <v>12</v>
+      </c>
+      <c r="F32" s="133" t="n">
+        <v>0.04013377926421405</v>
+      </c>
+      <c r="G32" s="123" t="n">
+        <v>166</v>
+      </c>
+      <c r="H32" s="133" t="n">
+        <v>0.5551839464882943</v>
+      </c>
+      <c r="I32" s="123" t="n">
+        <v>133</v>
+      </c>
+      <c r="J32" s="133" t="n">
+        <v>0.4448160535117057</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   CON ECT → Exportador neto</t>
+        </is>
+      </c>
+      <c r="B33" s="117" t="n">
+        <v>30</v>
+      </c>
+      <c r="C33" s="117" t="inlineStr"/>
+      <c r="D33" s="117" t="inlineStr"/>
+      <c r="E33" s="117" t="inlineStr"/>
+      <c r="F33" s="117" t="inlineStr"/>
+      <c r="G33" s="117" t="inlineStr"/>
+      <c r="H33" s="117" t="inlineStr"/>
+      <c r="I33" s="135" t="n">
+        <v>25</v>
+      </c>
+      <c r="J33" s="136" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   CON ECT → Importador neto</t>
+        </is>
+      </c>
+      <c r="B34" s="120" t="n">
+        <v>21</v>
+      </c>
+      <c r="C34" s="120" t="inlineStr"/>
+      <c r="D34" s="120" t="inlineStr"/>
+      <c r="E34" s="120" t="inlineStr"/>
+      <c r="F34" s="120" t="inlineStr"/>
+      <c r="G34" s="120" t="inlineStr"/>
+      <c r="H34" s="120" t="inlineStr"/>
+      <c r="I34" s="137" t="n">
+        <v>6</v>
+      </c>
+      <c r="J34" s="138" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   SIN ECT → Exportador neto</t>
+        </is>
+      </c>
+      <c r="B35" s="117" t="n">
+        <v>30</v>
+      </c>
+      <c r="C35" s="117" t="inlineStr"/>
+      <c r="D35" s="117" t="inlineStr"/>
+      <c r="E35" s="117" t="inlineStr"/>
+      <c r="F35" s="117" t="inlineStr"/>
+      <c r="G35" s="117" t="inlineStr"/>
+      <c r="H35" s="117" t="inlineStr"/>
+      <c r="I35" s="135" t="n">
+        <v>8</v>
+      </c>
+      <c r="J35" s="136" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   SIN ECT → Importador neto</t>
+        </is>
+      </c>
+      <c r="B36" s="120" t="n">
+        <v>269</v>
+      </c>
+      <c r="C36" s="120" t="inlineStr"/>
+      <c r="D36" s="120" t="inlineStr"/>
+      <c r="E36" s="120" t="inlineStr"/>
+      <c r="F36" s="120" t="inlineStr"/>
+      <c r="G36" s="120" t="inlineStr"/>
+      <c r="H36" s="120" t="inlineStr"/>
+      <c r="I36" s="137" t="n">
+        <v>125</v>
+      </c>
+      <c r="J36" s="138" t="n">
+        <v>0.4646840148698885</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="114" t="inlineStr">
+        <is>
+          <t>4. ÁRBITROS MÁS FRECUENTES (2000-2022)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="115" t="inlineStr">
+        <is>
+          <t>Presidente tribunal (árbitro dirimente)</t>
+        </is>
+      </c>
+      <c r="B40" s="115" t="inlineStr">
+        <is>
+          <t>N°</t>
+        </is>
+      </c>
+      <c r="C40" s="115" t="inlineStr"/>
+      <c r="D40" s="115" t="inlineStr">
+        <is>
+          <t>Nombrado por inversor</t>
+        </is>
+      </c>
+      <c r="E40" s="115" t="inlineStr">
+        <is>
+          <t>N°</t>
+        </is>
+      </c>
+      <c r="F40" s="115" t="inlineStr"/>
+      <c r="G40" s="115" t="inlineStr">
+        <is>
+          <t>Nombrado por estado</t>
+        </is>
+      </c>
+      <c r="H40" s="115" t="inlineStr">
+        <is>
+          <t>N°</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="139" t="inlineStr">
+        <is>
+          <t>Kaufmann-Kohler, G.</t>
+        </is>
+      </c>
+      <c r="B41" s="140" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" s="140" t="inlineStr"/>
+      <c r="D41" s="139" t="inlineStr">
+        <is>
+          <t>Alexandrov, S. A.</t>
+        </is>
+      </c>
+      <c r="E41" s="140" t="n">
+        <v>20</v>
+      </c>
+      <c r="F41" s="140" t="inlineStr"/>
+      <c r="G41" s="139" t="inlineStr">
+        <is>
+          <t>Stern, B.</t>
+        </is>
+      </c>
+      <c r="H41" s="140" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="141" t="inlineStr">
+        <is>
+          <t>Hanotiau, B.</t>
+        </is>
+      </c>
+      <c r="B42" s="142" t="n">
+        <v>13</v>
+      </c>
+      <c r="C42" s="142" t="inlineStr"/>
+      <c r="D42" s="141" t="inlineStr">
+        <is>
+          <t>Fortier, L. Y.</t>
+        </is>
+      </c>
+      <c r="E42" s="142" t="n">
+        <v>16</v>
+      </c>
+      <c r="F42" s="142" t="inlineStr"/>
+      <c r="G42" s="141" t="inlineStr">
+        <is>
+          <t>Thomas, J. C.</t>
+        </is>
+      </c>
+      <c r="H42" s="142" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="139" t="inlineStr">
+        <is>
+          <t>Fernández-Armesto, J.</t>
+        </is>
+      </c>
+      <c r="B43" s="140" t="n">
+        <v>12</v>
+      </c>
+      <c r="C43" s="140" t="inlineStr"/>
+      <c r="D43" s="139" t="inlineStr">
+        <is>
+          <t>Brower, C. N.</t>
+        </is>
+      </c>
+      <c r="E43" s="140" t="n">
+        <v>14</v>
+      </c>
+      <c r="F43" s="140" t="inlineStr"/>
+      <c r="G43" s="139" t="inlineStr">
+        <is>
+          <t>Douglas, Z.</t>
+        </is>
+      </c>
+      <c r="H43" s="140" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="141" t="inlineStr">
+        <is>
+          <t>Tercier, P.</t>
+        </is>
+      </c>
+      <c r="B44" s="142" t="n">
+        <v>10</v>
+      </c>
+      <c r="C44" s="142" t="inlineStr"/>
+      <c r="D44" s="141" t="inlineStr">
+        <is>
+          <t>Lalonde, M.</t>
+        </is>
+      </c>
+      <c r="E44" s="142" t="n">
+        <v>12</v>
+      </c>
+      <c r="F44" s="142" t="inlineStr"/>
+      <c r="G44" s="141" t="inlineStr">
+        <is>
+          <t>Sands, P.</t>
+        </is>
+      </c>
+      <c r="H44" s="142" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="139" t="inlineStr">
+        <is>
+          <t>Veeder, V. V.</t>
+        </is>
+      </c>
+      <c r="B45" s="140" t="n">
+        <v>10</v>
+      </c>
+      <c r="C45" s="140" t="inlineStr"/>
+      <c r="D45" s="139" t="inlineStr">
+        <is>
+          <t>Grigera Naón, H. A.</t>
+        </is>
+      </c>
+      <c r="E45" s="140" t="n">
+        <v>10</v>
+      </c>
+      <c r="F45" s="140" t="inlineStr"/>
+      <c r="G45" s="139" t="inlineStr">
+        <is>
+          <t>Dupuy, P.-M.</t>
+        </is>
+      </c>
+      <c r="H45" s="140" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="141" t="inlineStr">
+        <is>
+          <t>Lowe, V.</t>
+        </is>
+      </c>
+      <c r="B46" s="142" t="n">
+        <v>9</v>
+      </c>
+      <c r="C46" s="142" t="inlineStr"/>
+      <c r="D46" s="141" t="inlineStr">
+        <is>
+          <t>Hanotiau, B.</t>
+        </is>
+      </c>
+      <c r="E46" s="142" t="n">
+        <v>9</v>
+      </c>
+      <c r="F46" s="142" t="inlineStr"/>
+      <c r="G46" s="141" t="inlineStr">
+        <is>
+          <t>Vinuesa, R. E.</t>
+        </is>
+      </c>
+      <c r="H46" s="142" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="139" t="inlineStr">
+        <is>
+          <t>Fortier, L. Y.</t>
+        </is>
+      </c>
+      <c r="B47" s="140" t="n">
+        <v>9</v>
+      </c>
+      <c r="C47" s="140" t="inlineStr"/>
+      <c r="D47" s="139" t="inlineStr">
+        <is>
+          <t>Williams, D. A. R.</t>
+        </is>
+      </c>
+      <c r="E47" s="140" t="n">
+        <v>9</v>
+      </c>
+      <c r="F47" s="140" t="inlineStr"/>
+      <c r="G47" s="139" t="inlineStr">
+        <is>
+          <t>von Wobeser, C.</t>
+        </is>
+      </c>
+      <c r="H47" s="140" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="141" t="inlineStr">
+        <is>
+          <t>Zuleta, E.</t>
+        </is>
+      </c>
+      <c r="B48" s="142" t="n">
+        <v>8</v>
+      </c>
+      <c r="C48" s="142" t="inlineStr"/>
+      <c r="D48" s="141" t="inlineStr">
+        <is>
+          <t>Tawil, G. S.</t>
+        </is>
+      </c>
+      <c r="E48" s="142" t="n">
+        <v>7</v>
+      </c>
+      <c r="F48" s="142" t="inlineStr"/>
+      <c r="G48" s="141" t="inlineStr">
+        <is>
+          <t>Landau, T.</t>
+        </is>
+      </c>
+      <c r="H48" s="142" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="139" t="inlineStr">
+        <is>
+          <t>Rigo Sureda, A.</t>
+        </is>
+      </c>
+      <c r="B49" s="140" t="n">
+        <v>8</v>
+      </c>
+      <c r="C49" s="140" t="inlineStr"/>
+      <c r="D49" s="139" t="inlineStr">
+        <is>
+          <t>Pryles, M. C.</t>
+        </is>
+      </c>
+      <c r="E49" s="140" t="n">
+        <v>7</v>
+      </c>
+      <c r="F49" s="140" t="inlineStr"/>
+      <c r="G49" s="139" t="inlineStr">
+        <is>
+          <t>Knieper, R.</t>
+        </is>
+      </c>
+      <c r="H49" s="140" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="141" t="inlineStr">
+        <is>
+          <t>Binnie, I.</t>
+        </is>
+      </c>
+      <c r="B50" s="142" t="n">
+        <v>7</v>
+      </c>
+      <c r="C50" s="142" t="inlineStr"/>
+      <c r="D50" s="141" t="inlineStr">
+        <is>
+          <t>Orrego Vicuña, F.</t>
+        </is>
+      </c>
+      <c r="E50" s="142" t="n">
+        <v>7</v>
+      </c>
+      <c r="F50" s="142" t="inlineStr"/>
+      <c r="G50" s="141" t="inlineStr">
+        <is>
+          <t>Lowe, V.</t>
+        </is>
+      </c>
+      <c r="H50" s="142" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="139" t="inlineStr">
+        <is>
+          <t>van Houtte, H.</t>
+        </is>
+      </c>
+      <c r="B51" s="140" t="n">
+        <v>7</v>
+      </c>
+      <c r="C51" s="140" t="inlineStr"/>
+      <c r="D51" s="139" t="inlineStr">
+        <is>
+          <t>van den Berg, A. J.</t>
+        </is>
+      </c>
+      <c r="E51" s="140" t="n">
+        <v>6</v>
+      </c>
+      <c r="F51" s="140" t="inlineStr"/>
+      <c r="G51" s="139" t="inlineStr">
+        <is>
+          <t>Boisson de Chazournes, L.</t>
+        </is>
+      </c>
+      <c r="H51" s="140" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="141" t="inlineStr">
+        <is>
+          <t>Böckstiegel, K.-H.</t>
+        </is>
+      </c>
+      <c r="B52" s="142" t="n">
+        <v>7</v>
+      </c>
+      <c r="C52" s="142" t="inlineStr"/>
+      <c r="D52" s="141" t="inlineStr">
+        <is>
+          <t>Haigh, D.</t>
+        </is>
+      </c>
+      <c r="E52" s="142" t="n">
+        <v>6</v>
+      </c>
+      <c r="F52" s="142" t="inlineStr"/>
+      <c r="G52" s="141" t="inlineStr">
+        <is>
+          <t>Cremades, B. M.</t>
+        </is>
+      </c>
+      <c r="H52" s="142" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="139" t="inlineStr">
+        <is>
+          <t>Bull, C.</t>
+        </is>
+      </c>
+      <c r="B53" s="140" t="n">
+        <v>6</v>
+      </c>
+      <c r="C53" s="140" t="inlineStr"/>
+      <c r="D53" s="139" t="inlineStr">
+        <is>
+          <t>Beechey, J.</t>
+        </is>
+      </c>
+      <c r="E53" s="140" t="n">
+        <v>6</v>
+      </c>
+      <c r="F53" s="140" t="inlineStr"/>
+      <c r="G53" s="139" t="inlineStr">
+        <is>
+          <t>van den Berg, A. J.</t>
+        </is>
+      </c>
+      <c r="H53" s="140" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="141" t="inlineStr">
+        <is>
+          <t>Derains, Y.</t>
+        </is>
+      </c>
+      <c r="B54" s="142" t="n">
+        <v>6</v>
+      </c>
+      <c r="C54" s="142" t="inlineStr"/>
+      <c r="D54" s="141" t="inlineStr">
+        <is>
+          <t>Rowley, J. W.</t>
+        </is>
+      </c>
+      <c r="E54" s="142" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" s="142" t="inlineStr"/>
+      <c r="G54" s="141" t="inlineStr">
+        <is>
+          <t>Reisman, W. M.</t>
+        </is>
+      </c>
+      <c r="H54" s="142" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="139" t="inlineStr">
+        <is>
+          <t>Mourre, A.</t>
+        </is>
+      </c>
+      <c r="B55" s="140" t="n">
+        <v>6</v>
+      </c>
+      <c r="C55" s="140" t="inlineStr"/>
+      <c r="D55" s="139" t="inlineStr">
+        <is>
+          <t>Orrego Vicuña, F. (replaced)</t>
+        </is>
+      </c>
+      <c r="E55" s="140" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" s="140" t="inlineStr"/>
+      <c r="G55" s="139" t="inlineStr">
+        <is>
+          <t>Malintoppi, L.</t>
+        </is>
+      </c>
+      <c r="H55" s="140" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="107" t="inlineStr">
+        <is>
+          <t>⚑ Brigitte Stern (52 veces nombrada por estados demandados) es la árbitro más usada como defensa estatal. Especialista en derecho internacional público.</t>
+        </is>
+      </c>
+      <c r="B57" s="112" t="n"/>
+      <c r="C57" s="112" t="n"/>
+      <c r="D57" s="112" t="n"/>
+      <c r="E57" s="112" t="n"/>
+      <c r="F57" s="112" t="n"/>
+      <c r="G57" s="112" t="n"/>
+      <c r="H57" s="112" t="n"/>
+      <c r="I57" s="112" t="n"/>
+      <c r="J57" s="110" t="n"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="114" t="inlineStr">
+        <is>
+          <t>5. ANULACIONES POST-LAUDO (ICSID)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="115" t="inlineStr">
+        <is>
+          <t>Estado del proceso</t>
+        </is>
+      </c>
+      <c r="B60" s="115" t="inlineStr">
+        <is>
+          <t>N° casos</t>
+        </is>
+      </c>
+      <c r="C60" s="115" t="inlineStr">
+        <is>
+          <t>Condenas originales</t>
+        </is>
+      </c>
+      <c r="D60" s="115" t="inlineStr">
+        <is>
+          <t>Absoluciones originales</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="143" t="inlineStr">
+        <is>
+          <t>Anulados totalmente</t>
+        </is>
+      </c>
+      <c r="B61" s="144" t="n">
+        <v>5</v>
+      </c>
+      <c r="C61" s="144" t="n">
+        <v>2</v>
+      </c>
+      <c r="D61" s="144" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="145" t="inlineStr">
+        <is>
+          <t>Anulados parcialmente</t>
+        </is>
+      </c>
+      <c r="B62" s="146" t="n">
+        <v>10</v>
+      </c>
+      <c r="C62" s="146" t="n">
+        <v>8</v>
+      </c>
+      <c r="D62" s="146" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="147" t="inlineStr">
+        <is>
+          <t>Confirmados (upheld)</t>
+        </is>
+      </c>
+      <c r="B63" s="148" t="n">
+        <v>94</v>
+      </c>
+      <c r="C63" s="148" t="n">
+        <v>59</v>
+      </c>
+      <c r="D63" s="148" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="149" t="inlineStr">
+        <is>
+          <t>Pendientes</t>
+        </is>
+      </c>
+      <c r="B64" s="131" t="n">
+        <v>36</v>
+      </c>
+      <c r="C64" s="131" t="n">
+        <v>25</v>
+      </c>
+      <c r="D64" s="131" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="150" t="inlineStr">
+        <is>
+          <t>Discontinuados</t>
+        </is>
+      </c>
+      <c r="B65" s="123" t="n">
+        <v>32</v>
+      </c>
+      <c r="C65" s="123" t="n">
+        <v>18</v>
+      </c>
+      <c r="D65" s="123" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="114" t="inlineStr">
+        <is>
+          <t>6. CASOS CONFIDENCIALES — Laudos sin acceso público (limitación metodológica)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="151" t="inlineStr">
+        <is>
+          <t>Total casos sin laudo accesible: 25</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="115" t="inlineStr">
+        <is>
+          <t>Caso</t>
+        </is>
+      </c>
+      <c r="B70" s="115" t="inlineStr">
+        <is>
+          <t>Estado demandado</t>
+        </is>
+      </c>
+      <c r="C70" s="115" t="inlineStr">
+        <is>
+          <t>Clasificación</t>
+        </is>
+      </c>
+      <c r="D70" s="115" t="inlineStr">
+        <is>
+          <t>Resultado (UNCTAD)</t>
+        </is>
+      </c>
+      <c r="E70" s="115" t="inlineStr">
+        <is>
+          <t>Año</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="147" t="inlineStr">
+        <is>
+          <t>Pavilniu and Modus v. Belarus</t>
+        </is>
+      </c>
+      <c r="B71" s="147" t="inlineStr">
+        <is>
+          <t>Belarus</t>
+        </is>
+      </c>
+      <c r="C71" s="148" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D71" s="147" t="inlineStr">
+        <is>
+          <t>No - ganó el Estado</t>
+        </is>
+      </c>
+      <c r="E71" s="148" t="n">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="147" t="inlineStr">
+        <is>
+          <t>Silver Ridge v. Italy</t>
+        </is>
+      </c>
+      <c r="B72" s="147" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C72" s="148" t="inlineStr">
+        <is>
+          <t>Exportador neto</t>
+        </is>
+      </c>
+      <c r="D72" s="147" t="inlineStr">
+        <is>
+          <t>No - ganó el Estado</t>
+        </is>
+      </c>
+      <c r="E72" s="148" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="147" t="inlineStr">
+        <is>
+          <t>SGRF v. Bulgaria</t>
+        </is>
+      </c>
+      <c r="B73" s="147" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C73" s="148" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D73" s="147" t="inlineStr">
+        <is>
+          <t>No - ganó el Estado</t>
+        </is>
+      </c>
+      <c r="E73" s="148" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="147" t="inlineStr">
+        <is>
+          <t>ENERGO-PRO v. Bulgaria</t>
+        </is>
+      </c>
+      <c r="B74" s="147" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C74" s="148" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D74" s="147" t="inlineStr">
+        <is>
+          <t>No - ganó el Estado</t>
+        </is>
+      </c>
+      <c r="E74" s="148" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="147" t="inlineStr">
+        <is>
+          <t>Belegging-Maatschappij “Far East” v. Austria</t>
+        </is>
+      </c>
+      <c r="B75" s="147" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="C75" s="148" t="inlineStr">
+        <is>
+          <t>Exportador neto</t>
+        </is>
+      </c>
+      <c r="D75" s="147" t="inlineStr">
+        <is>
+          <t>No - ganó el Estado</t>
+        </is>
+      </c>
+      <c r="E75" s="148" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="147" t="inlineStr">
+        <is>
+          <t>Champion Holding Company and others v. Egypt</t>
+        </is>
+      </c>
+      <c r="B76" s="147" t="inlineStr">
+        <is>
+          <t>Egypt</t>
+        </is>
+      </c>
+      <c r="C76" s="148" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D76" s="147" t="inlineStr">
+        <is>
+          <t>No - ganó el Estado</t>
+        </is>
+      </c>
+      <c r="E76" s="148" t="n">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="147" t="inlineStr">
+        <is>
+          <t>América Móvil v. Colombia</t>
+        </is>
+      </c>
+      <c r="B77" s="147" t="inlineStr">
+        <is>
+          <t>Colombia</t>
+        </is>
+      </c>
+      <c r="C77" s="148" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D77" s="147" t="inlineStr">
+        <is>
+          <t>No - ganó el Estado</t>
+        </is>
+      </c>
+      <c r="E77" s="148" t="n">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="147" t="inlineStr">
+        <is>
+          <t>HEP v. Slovenia</t>
+        </is>
+      </c>
+      <c r="B78" s="147" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="C78" s="148" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D78" s="147" t="inlineStr">
+        <is>
+          <t>No - ganó el Estado</t>
+        </is>
+      </c>
+      <c r="E78" s="148" t="n">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="147" t="inlineStr">
+        <is>
+          <t>Al Ramahi v. Hungary</t>
+        </is>
+      </c>
+      <c r="B79" s="147" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="C79" s="148" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D79" s="147" t="inlineStr">
+        <is>
+          <t>No - ganó el Estado</t>
+        </is>
+      </c>
+      <c r="E79" s="148" t="n">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="147" t="inlineStr">
+        <is>
+          <t>LTME and Madamobil v. Madagascar</t>
+        </is>
+      </c>
+      <c r="B80" s="147" t="inlineStr">
+        <is>
+          <t>Madagascar</t>
+        </is>
+      </c>
+      <c r="C80" s="148" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D80" s="147" t="inlineStr">
+        <is>
+          <t>No - ganó el Estado</t>
+        </is>
+      </c>
+      <c r="E80" s="148" t="n">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="147" t="inlineStr">
+        <is>
+          <t>Eutelsat v. Mexico</t>
+        </is>
+      </c>
+      <c r="B81" s="147" t="inlineStr">
+        <is>
+          <t>Mexico</t>
+        </is>
+      </c>
+      <c r="C81" s="148" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D81" s="147" t="inlineStr">
+        <is>
+          <t>No - ganó el Estado</t>
+        </is>
+      </c>
+      <c r="E81" s="148" t="n">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="147" t="inlineStr">
+        <is>
+          <t>Axiata and Ncell v. Nepal</t>
+        </is>
+      </c>
+      <c r="B82" s="147" t="inlineStr">
+        <is>
+          <t>Nepal</t>
+        </is>
+      </c>
+      <c r="C82" s="148" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D82" s="147" t="inlineStr">
+        <is>
+          <t>No - ganó el Estado</t>
+        </is>
+      </c>
+      <c r="E82" s="148" t="n">
+        <v>2019</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="147" t="inlineStr">
+        <is>
+          <t>Kimberly-Clark v. Venezuela</t>
+        </is>
+      </c>
+      <c r="B83" s="147" t="inlineStr">
+        <is>
+          <t>Venezuela, Bolivarian Republic of</t>
+        </is>
+      </c>
+      <c r="C83" s="148" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D83" s="147" t="inlineStr">
+        <is>
+          <t>No - ganó el Estado</t>
+        </is>
+      </c>
+      <c r="E83" s="148" t="n">
+        <v>2018</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="147" t="inlineStr">
+        <is>
+          <t>Samsung v. Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B84" s="147" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="C84" s="148" t="inlineStr">
+        <is>
+          <t>Exportador neto</t>
+        </is>
+      </c>
+      <c r="D84" s="147" t="inlineStr">
+        <is>
+          <t>No - ganó el Estado</t>
+        </is>
+      </c>
+      <c r="E84" s="148" t="n">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="143" t="inlineStr">
+        <is>
+          <t>Cyprus Popular Bank v. Greece</t>
+        </is>
+      </c>
+      <c r="B85" s="143" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C85" s="144" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D85" s="143" t="inlineStr">
+        <is>
+          <t>Sí con daños</t>
+        </is>
+      </c>
+      <c r="E85" s="144" t="n">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="143" t="inlineStr">
+        <is>
+          <t>United Agencies v. Algeria (I)</t>
+        </is>
+      </c>
+      <c r="B86" s="143" t="inlineStr">
+        <is>
+          <t>Algeria</t>
+        </is>
+      </c>
+      <c r="C86" s="144" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D86" s="143" t="inlineStr">
+        <is>
+          <t>Sí con daños</t>
+        </is>
+      </c>
+      <c r="E86" s="144" t="n">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="143" t="inlineStr">
+        <is>
+          <t>JGC v. Spain</t>
+        </is>
+      </c>
+      <c r="B87" s="143" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C87" s="144" t="inlineStr">
+        <is>
+          <t>Exportador neto</t>
+        </is>
+      </c>
+      <c r="D87" s="143" t="inlineStr">
+        <is>
+          <t>Sí con daños</t>
+        </is>
+      </c>
+      <c r="E87" s="144" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="143" t="inlineStr">
+        <is>
+          <t>Agroinsumos Ibero-Americanos and others v. Ve</t>
+        </is>
+      </c>
+      <c r="B88" s="143" t="inlineStr">
+        <is>
+          <t>Venezuela, Bolivarian Republic of</t>
+        </is>
+      </c>
+      <c r="C88" s="144" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D88" s="143" t="inlineStr">
+        <is>
+          <t>Sí con daños</t>
+        </is>
+      </c>
+      <c r="E88" s="144" t="n">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="143" t="inlineStr">
+        <is>
+          <t>Aktau Petrol v. Kazakhstan</t>
+        </is>
+      </c>
+      <c r="B89" s="143" t="inlineStr">
+        <is>
+          <t>Kazakhstan</t>
+        </is>
+      </c>
+      <c r="C89" s="144" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D89" s="143" t="inlineStr">
+        <is>
+          <t>Sí con daños</t>
+        </is>
+      </c>
+      <c r="E89" s="144" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="143" t="inlineStr">
+        <is>
+          <t>Kunsttrans v. Serbia</t>
+        </is>
+      </c>
+      <c r="B90" s="143" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="C90" s="144" t="inlineStr">
+        <is>
+          <t>Exportador neto</t>
+        </is>
+      </c>
+      <c r="D90" s="143" t="inlineStr">
+        <is>
+          <t>Sí con daños</t>
+        </is>
+      </c>
+      <c r="E90" s="144" t="n">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="143" t="inlineStr">
+        <is>
+          <t>ARVI and SANITEX v. Serbia</t>
+        </is>
+      </c>
+      <c r="B91" s="143" t="inlineStr">
+        <is>
+          <t>Serbia</t>
+        </is>
+      </c>
+      <c r="C91" s="144" t="inlineStr">
+        <is>
+          <t>Exportador neto</t>
+        </is>
+      </c>
+      <c r="D91" s="143" t="inlineStr">
+        <is>
+          <t>Sí con daños</t>
+        </is>
+      </c>
+      <c r="E91" s="144" t="n">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="143" t="inlineStr">
+        <is>
+          <t>El Jaouni v. Lebanon</t>
+        </is>
+      </c>
+      <c r="B92" s="143" t="inlineStr">
+        <is>
+          <t>Lebanon</t>
+        </is>
+      </c>
+      <c r="C92" s="144" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D92" s="143" t="inlineStr">
+        <is>
+          <t>Sí con daños</t>
+        </is>
+      </c>
+      <c r="E92" s="144" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="143" t="inlineStr">
+        <is>
+          <t>JSC Tashkent and others v. Kyrgyzstan</t>
+        </is>
+      </c>
+      <c r="B93" s="143" t="inlineStr">
+        <is>
+          <t>Kyrgyzstan</t>
+        </is>
+      </c>
+      <c r="C93" s="144" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D93" s="143" t="inlineStr">
+        <is>
+          <t>Sí con daños</t>
+        </is>
+      </c>
+      <c r="E93" s="144" t="n">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="145" t="inlineStr">
+        <is>
+          <t>B3 Croatian Courier v. Croatia</t>
+        </is>
+      </c>
+      <c r="B94" s="145" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="C94" s="146" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D94" s="145" t="inlineStr">
+        <is>
+          <t>Sí sin daños</t>
+        </is>
+      </c>
+      <c r="E94" s="146" t="n">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="145" t="inlineStr">
+        <is>
+          <t>Amlyn v. Croatia</t>
+        </is>
+      </c>
+      <c r="B95" s="145" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="C95" s="146" t="inlineStr">
+        <is>
+          <t>Importador neto</t>
+        </is>
+      </c>
+      <c r="D95" s="145" t="inlineStr">
+        <is>
+          <t>Sí sin daños</t>
+        </is>
+      </c>
+      <c r="E95" s="146" t="n">
+        <v>2016</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A3:J3"/>
+    <mergeCell ref="A39:J39"/>
+    <mergeCell ref="A29:J29"/>
+    <mergeCell ref="A59:J59"/>
+    <mergeCell ref="A57:J57"/>
+    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="A68:J68"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1529,6 +6064,8 @@
           <t>Estados exportadores netos: mayor tasa de condena</t>
         </is>
       </c>
+      <c r="B37" s="108" t="n"/>
+      <c r="C37" s="109" t="n"/>
       <c r="D37" s="75" t="inlineStr">
         <is>
           <t>55.0% vs 45.6%</t>
@@ -1539,6 +6076,7 @@
           <t>Contra-intuitivo según la hipótesis inicial</t>
         </is>
       </c>
+      <c r="F37" s="109" t="n"/>
     </row>
     <row r="38" ht="25" customHeight="1">
       <c r="A38" s="74" t="inlineStr">
@@ -1546,6 +6084,8 @@
           <t>Inversores exportadores: mayor tasa de condena</t>
         </is>
       </c>
+      <c r="B38" s="108" t="n"/>
+      <c r="C38" s="109" t="n"/>
       <c r="D38" s="75" t="inlineStr">
         <is>
           <t>47.4% vs 35.4%</t>
@@ -1556,6 +6096,7 @@
           <t>Los inversores de países ricos ganan más</t>
         </is>
       </c>
+      <c r="F38" s="109" t="n"/>
     </row>
     <row r="39" ht="25" customHeight="1">
       <c r="A39" s="74" t="inlineStr">
@@ -1563,6 +6104,8 @@
           <t>España ⚠️: 25 casos, 92% tasa de condena</t>
         </is>
       </c>
+      <c r="B39" s="108" t="n"/>
+      <c r="C39" s="109" t="n"/>
       <c r="D39" s="75" t="inlineStr">
         <is>
           <t>Clasificación BM: Exportadora</t>
@@ -1573,6 +6116,7 @@
           <t>Requiere verificación UNCTAD — usuario cree es importadora</t>
         </is>
       </c>
+      <c r="F39" s="109" t="n"/>
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="74" t="inlineStr">
@@ -1580,6 +6124,8 @@
           <t>Venezuela: 26 casos como demandada</t>
         </is>
       </c>
+      <c r="B40" s="108" t="n"/>
+      <c r="C40" s="109" t="n"/>
       <c r="D40" s="75" t="inlineStr">
         <is>
           <t>65.4% tasa condena</t>
@@ -1590,6 +6136,7 @@
           <t>Mayor demandada en América Latina</t>
         </is>
       </c>
+      <c r="F40" s="109" t="n"/>
     </row>
     <row r="41" ht="25" customHeight="1">
       <c r="A41" s="74" t="inlineStr">
@@ -1597,6 +6144,8 @@
           <t>EE.UU.: 62 casos como inversor</t>
         </is>
       </c>
+      <c r="B41" s="108" t="n"/>
+      <c r="C41" s="109" t="n"/>
       <c r="D41" s="75" t="inlineStr">
         <is>
           <t>37.1% tasa condena</t>
@@ -1607,6 +6156,7 @@
           <t>Mayor inversor demandante del período</t>
         </is>
       </c>
+      <c r="F41" s="109" t="n"/>
     </row>
     <row r="42" ht="25" customHeight="1">
       <c r="A42" s="74" t="inlineStr">
@@ -1614,6 +6164,8 @@
           <t>Países Bajos: 28 casos, treaty shopping</t>
         </is>
       </c>
+      <c r="B42" s="108" t="n"/>
+      <c r="C42" s="109" t="n"/>
       <c r="D42" s="75" t="inlineStr">
         <is>
           <t>46.4% tasa condena</t>
@@ -1624,6 +6176,7 @@
           <t>Holdings holandeses amplifican la exposición</t>
         </is>
       </c>
+      <c r="F42" s="109" t="n"/>
     </row>
     <row r="43" ht="25" customHeight="1">
       <c r="A43" s="74" t="inlineStr">
@@ -1631,6 +6184,8 @@
           <t>Total: 350 laudos analizados</t>
         </is>
       </c>
+      <c r="B43" s="108" t="n"/>
+      <c r="C43" s="109" t="n"/>
       <c r="D43" s="75" t="inlineStr">
         <is>
           <t>164 condenas (46.9%)</t>
@@ -1641,6 +6196,7 @@
           <t>Período 2000-2022, 23 años</t>
         </is>
       </c>
+      <c r="F43" s="109" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="19">
@@ -1668,7 +6224,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5757,7 +10313,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11092,7 +15648,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
